--- a/data/b2_primavera/B2 Primavera 08-2026.xlsx
+++ b/data/b2_primavera/B2 Primavera 08-2026.xlsx
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1085.69</v>
+        <v>1125.97</v>
       </c>
     </row>
     <row r="3">
@@ -4990,43 +4990,43 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>57969.06</v>
+        <v>58549.52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>2893.19</v>
+        <v>3840.97</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Aluguel do imóvel</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>3924.13</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="6">
@@ -5035,52 +5035,52 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Aluguel do imóvel</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>14000</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>3600</v>
+        <v>1304.43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46246</v>
+        <v>46249</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1070.2</v>
+        <v>8616.639999999999</v>
       </c>
     </row>
     <row r="9">
@@ -5089,16 +5089,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>8435.15</v>
+        <v>3526.55</v>
       </c>
     </row>
     <row r="10">
@@ -5107,16 +5107,16 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Tarifas bancárias</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>3773.89</v>
+        <v>1133.33</v>
       </c>
     </row>
     <row r="11">
@@ -5134,48 +5134,48 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>4153.74</v>
+        <v>3860.69</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Aferição das bombas — Inmetro</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>1335.8</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Troca de filtros das bombas</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>2221.37</v>
+        <v>20128.21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46252</v>
+        <v>46255</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -5184,16 +5184,16 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Aferição das bombas — Inmetro</t>
+          <t>Manutenção do compressor de ar</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>4250</v>
+        <v>3793.38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46253</v>
+        <v>46257</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -5202,65 +5202,65 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>1117.87</v>
+        <v>1550.78</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46254</v>
+        <v>46257</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>20136.78</v>
+        <v>3719.27</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uniformes e EPI</t>
+          <t>Troca de filtros das bombas</t>
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>835.64</v>
+        <v>2182.14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46257</v>
+        <v>46260</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>3929.41</v>
+        <v>1176.67</v>
       </c>
     </row>
     <row r="19">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>3884.59</v>
+        <v>4117.41</v>
       </c>
     </row>
     <row r="20">
@@ -5296,7 +5296,7 @@
         </is>
       </c>
       <c r="D20" s="16" t="n">
-        <v>547.62</v>
+        <v>577.67</v>
       </c>
     </row>
   </sheetData>
